--- a/site/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Worker Management</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01K4ABWX5CN4ZFSY5ETKDSK0T8</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K4ABWX5CN4ZFSY5ETKDSK0T8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Monitored Provision</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KC3Y89NAAVSS7TXVNZXTEANX</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KC3Y89NAAVSS7TXVNZXTEANX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,320 +759,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Post-Setup Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Monitored Provisioning Notification</t>
+          <t>Integration Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KEH0NNX6H4M85JXE0FX4J916</t>
+          <t>h_01KJ7MRNM94P5VN9TZT086EYRJ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KEH0NNX6H4M85JXE0FX4J916</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Log Insights Settings</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Attribute Map</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Mapping Custom Attributes</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Group Rules</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KJ53Y3H4BWX0QQW00JSQW5WC</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Create Custom Attributes in Okta</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Map Custom Attribute to Okta Profile</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ADP Workforce Now Worker Attributes</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h_01HXV5081PWKBEKH540JBRRMQM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01HXV5081PWKBEKH540JBRRMQM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Run Integration</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Troubleshooting</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>h_01KFFVZ8N3N820WBEPX37HT843</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KFFVZ8N3N820WBEPX37HT843</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>FAQs</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>h_01KADNT38N98M887JSH86ZKKVY</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KADNT38N98M887JSH86ZKKVY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KJ7MRNM94P5VN9TZT086EYRJ</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Global Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01KJ9RSC97232HKQ93FNN8QSB1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KJ9RSC97232HKQ93FNN8QSB1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,41 +649,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,76 +759,98 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Post-Setup Configuration</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Post-Setup Configuration</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01K7H3FBM0V1D99VEW60RCKMFX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Integration Execution</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>h_01KJ7MRNM94P5VN9TZT086EYRJ</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KJ7MRNM94P5VN9TZT086EYRJ</t>
         </is>

--- a/site/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/headings.xlsx
@@ -661,29 +661,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Onboarding Ticket</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>h_01KJ9TWD6QFKDRCFACREM8AT98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KJ9TWD6QFKDRCFACREM8AT98</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Offboarding Ticket</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01KJ9TWJ5CKMNZY8TXB038K889</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-HaloPSA-Joiner-and-Leaver-Ticket-Creation-Integration-Guide/#h_01KJ9TWJ5CKMNZY8TXB038K889</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
